--- a/data/trans_camb/BARTHEL_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Clase-trans_camb.xlsx
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,35</t>
+          <t>-6,99; 18,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 9,61</t>
+          <t>-9,95; 6,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,79</t>
+          <t>-8,92; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 13,46</t>
+          <t>-12,1; 17,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 15,19</t>
+          <t>-15,8; 11,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 15,66</t>
+          <t>-14,64; 8,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 5,66</t>
+          <t>-6,5; 12,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 8,1</t>
+          <t>-7,94; 6,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 6,99</t>
+          <t>-6,69; 5,18</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-2,09%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-14,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,21%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,3%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>-4,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-1,87%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-9,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,33%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 7,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 10,76</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 10,11</t>
+          <t>-75,38; 295,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 15,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 18,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 19,54</t>
+          <t>-85,74; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 6,17</t>
+          <t>-85,55; 641,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 8,87</t>
+          <t>-81,92; 296,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,88</t>
+          <t>-60,88; 253,48</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-7,54</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-11,96</t>
+          <t>11,96</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,6</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>-3,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-6,41</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>-7,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,79</t>
+          <t>10,79</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>2,9</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -0,21</t>
+          <t>0,54; 20,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,19; -3,26</t>
+          <t>3,71; 23,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,12</t>
+          <t>-0,14; 11,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 34,28</t>
+          <t>-32,28; 22,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 23,01</t>
+          <t>-26,8; 41,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 38,67</t>
+          <t>-40,44; 8,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 4,03</t>
+          <t>-3,56; 16,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,54; -0,44</t>
+          <t>0,59; 22,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 5,54</t>
+          <t>-5,14; 8,61</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>468,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-12,15%</t>
+          <t>742,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,69%</t>
+          <t>347,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>-14,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-8,07%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>-38,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-5,38%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,49%</t>
+          <t>176,76%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,09%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,98; -0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -3,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 0,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 61,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 33,8</t>
+          <t>-100,0; 713,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 73,63</t>
+          <t>-81,01; 158,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 4,16</t>
+          <t>-54,54; 790,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,43; -0,5</t>
+          <t>-16,56; 1038,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 6,28</t>
+          <t>-43,34; 458,63</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>-2,7</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,63</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,51</t>
+          <t>4,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 8,24</t>
+          <t>-8,95; 8,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 7,72</t>
+          <t>-7,73; 7,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 3,79</t>
+          <t>-4,05; 12,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 19,24</t>
+          <t>-18,98; 20,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 22,63</t>
+          <t>-23,92; 14,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 19,98</t>
+          <t>-17,81; 16,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 5,98</t>
+          <t>-6,28; 10,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 7,62</t>
+          <t>-7,84; 7,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 3,95</t>
+          <t>-3,45; 11,67</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-0,19%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-5,12%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,4%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>-14,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,0%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-1,81%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,1%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 9,43</t>
+          <t>-67,03; 217,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 8,97</t>
+          <t>-58,08; 195,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 4,33</t>
+          <t>-30,7; 295,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 30,21</t>
+          <t>-61,69; 378,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 33,65</t>
+          <t>-77,22; 233,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 31,61</t>
+          <t>-55,46; 306,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 7,15</t>
+          <t>-41,46; 156,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 9,13</t>
+          <t>-49,55; 117,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 4,8</t>
+          <t>-23,35; 182,26</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-12,31</t>
+          <t>12,31</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,26</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-14,69</t>
+          <t>14,69</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-12,38</t>
+          <t>12,38</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34</t>
+          <t>-2,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-12,8</t>
+          <t>12,8</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,18</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,52</t>
+          <t>2,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -5,49</t>
+          <t>5,87; 18,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 2,93</t>
+          <t>-3,34; 6,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -3,63</t>
+          <t>3,82; 14,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -2,43</t>
+          <t>2,76; 27,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,45; -2,27</t>
+          <t>1,97; 24,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 16,41</t>
+          <t>-15,45; 9,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,05; -7,38</t>
+          <t>6,75; 18,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -0,31</t>
+          <t>0,14; 10,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 6,85</t>
+          <t>-6,38; 10,22</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-13,47%</t>
+          <t>142,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-1,85%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,14%</t>
+          <t>107,55%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-16,07%</t>
+          <t>171,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-13,55%</t>
+          <t>144,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>-27,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-14,01%</t>
+          <t>148,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-5,67%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,76%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,72; -6,21</t>
+          <t>49,88; 292,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,31</t>
+          <t>-32,37; 103,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -4,14</t>
+          <t>32,36; 231,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,57; -2,81</t>
+          <t>5,31; 593,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -2,72</t>
+          <t>5,28; 522,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 20,52</t>
+          <t>-86,52; 142,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,47; -8,27</t>
+          <t>61,14; 289,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,36</t>
+          <t>-1,94; 161,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 7,77</t>
+          <t>-59,18; 130,48</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-5,66</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-14,85</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,42</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>-10,49</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,13</t>
+          <t>7,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 9,02</t>
+          <t>-9,36; 12,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 4,58</t>
+          <t>-5,37; 15,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 9,25</t>
+          <t>-10,73; 9,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-24,86; -3,07</t>
+          <t>3,43; 24,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 8,0</t>
+          <t>-7,63; 14,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 1,15</t>
+          <t>-0,38; 17,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -2,07</t>
+          <t>2,42; 18,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 5,4</t>
+          <t>-5,19; 11,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,8</t>
+          <t>-0,78; 14,42</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-2,63%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-6,52%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,19%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-18,37%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-11,65%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-12,64%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-4,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-8,58%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 11,76</t>
+          <t>-49,0; 183,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 5,7</t>
+          <t>-29,43; 229,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 11,56</t>
+          <t>-49,08; 158,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,31; -4,42</t>
+          <t>13,29; 196,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 10,8</t>
+          <t>-30,44; 112,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 1,55</t>
+          <t>-2,24; 152,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,62; -2,83</t>
+          <t>8,92; 155,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 7,24</t>
+          <t>-24,27; 90,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 1,13</t>
+          <t>-5,16; 127,26</t>
         </is>
       </c>
     </row>
@@ -1714,37 +1714,37 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-34,08</t>
+          <t>34,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-11,38</t>
+          <t>11,38</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-10,54</t>
+          <t>10,54</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,41</t>
+          <t>13,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-11,37</t>
+          <t>11,37</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-10,65</t>
+          <t>10,65</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-13,59</t>
+          <t>13,59</t>
         </is>
       </c>
     </row>
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 0,0</t>
+          <t>0,0; 71,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,13; -5,8</t>
+          <t>6,04; 17,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,93; -4,66</t>
+          <t>4,25; 15,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -8,55</t>
+          <t>8,63; 18,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-17,1; -6,02</t>
+          <t>6,4; 17,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -4,51</t>
+          <t>5,13; 16,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,52; -8,52</t>
+          <t>8,8; 18,36</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1820,37 +1820,37 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-34,08%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-13,08%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-12,11%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-15,42%</t>
+          <t>102,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>-13,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-12,23%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-15,61%</t>
+          <t>105,19%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -6,85</t>
+          <t>38,47; 166,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,94; -5,51</t>
+          <t>26,66; 149,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -10,05</t>
+          <t>53,54; 174,98</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,13; -7,14</t>
+          <t>41,46; 169,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -5,29</t>
+          <t>33,34; 158,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,86; -10,12</t>
+          <t>54,52; 177,88</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-6,97</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-3,9</t>
+          <t>3,9</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-12,35</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-8,39</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,72</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-10,01</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-6,4</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>5,07</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -3,0</t>
+          <t>2,94; 10,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -0,42</t>
+          <t>0,23; 7,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -1,88</t>
+          <t>1,79; 8,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,62; -7,64</t>
+          <t>7,86; 16,41</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-12,7; -3,83</t>
+          <t>4,19; 12,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 4,34</t>
+          <t>-5,12; 10,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -7,2</t>
+          <t>7,18; 13,13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -3,55</t>
+          <t>3,37; 9,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 0,84</t>
+          <t>-1,12; 8,32</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-7,57%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-4,24%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-5,5%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-14,27%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-9,69%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,46%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-11,26%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-7,2%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-5,71%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -3,27</t>
+          <t>30,97; 170,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -0,51</t>
+          <t>1,2; 110,92</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -2,13</t>
+          <t>16,88; 131,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -9,17</t>
+          <t>48,14; 146,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,48; -4,56</t>
+          <t>24,6; 106,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 5,11</t>
+          <t>-35,01; 83,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -8,25</t>
+          <t>55,76; 131,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -4,06</t>
+          <t>27,21; 93,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 1,04</t>
+          <t>-7,57; 82,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/BARTHEL_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 18,16</t>
+          <t>-7,19; 18,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 6,43</t>
+          <t>-10,08; 7,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 5,26</t>
+          <t>-9,86; 4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 17,93</t>
+          <t>-11,92; 17,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 11,15</t>
+          <t>-13,41; 13,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 8,31</t>
+          <t>-15,89; 7,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 12,69</t>
+          <t>-6,37; 12,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 6,07</t>
+          <t>-7,82; 6,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 5,18</t>
+          <t>-8,24; 4,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>-5,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>-0,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>-1,97%</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,38; 295,47</t>
+          <t>-80,84; 285,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,74; —</t>
+          <t>-84,4; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 641,81</t>
+          <t>-78,46; 481,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,92; 296,9</t>
+          <t>-81,6; 380,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 253,48</t>
+          <t>-63,6; 194,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,9</t>
+          <t>-8,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,03</t>
+          <t>0,26; 21,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 23,25</t>
+          <t>4,36; 23,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 11,57</t>
+          <t>-0,15; 10,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,28; 22,14</t>
+          <t>-32,34; 25,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 41,08</t>
+          <t>-27,93; 39,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 8,64</t>
+          <t>-37,49; 8,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 16,21</t>
+          <t>-4,11; 15,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 22,76</t>
+          <t>0,36; 22,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 8,61</t>
+          <t>-5,45; 8,59</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>347,46%</t>
+          <t>326,18%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,4%</t>
+          <t>-40,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 713,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,01; 158,93</t>
+          <t>-83,37; 143,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 790,59</t>
+          <t>-59,58; 660,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 1038,11</t>
+          <t>-23,61; 985,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 458,63</t>
+          <t>-49,35; 459,81</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>2,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>4,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 8,1</t>
+          <t>-8,03; 9,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 7,76</t>
+          <t>-6,53; 8,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 12,23</t>
+          <t>-5,05; 11,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 20,04</t>
+          <t>-19,41; 19,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 14,87</t>
+          <t>-23,76; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 16,75</t>
+          <t>-18,33; 17,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 10,05</t>
+          <t>-7,61; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 7,53</t>
+          <t>-8,05; 7,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 11,67</t>
+          <t>-3,94; 11,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-67,03; 217,16</t>
+          <t>-62,24; 222,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,08; 195,68</t>
+          <t>-51,78; 212,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 295,57</t>
+          <t>-38,04; 269,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 378,11</t>
+          <t>-62,65; 344,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,22; 233,15</t>
+          <t>-79,22; 275,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 306,75</t>
+          <t>-52,69; 300,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 156,84</t>
+          <t>-48,17; 143,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 117,71</t>
+          <t>-51,19; 132,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 182,26</t>
+          <t>-24,32; 191,32</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>8,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>8,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,87</t>
+          <t>6,0; 19,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 6,66</t>
+          <t>-3,33; 7,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,44</t>
+          <t>4,17; 14,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 27,6</t>
+          <t>2,63; 26,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 24,31</t>
+          <t>1,38; 24,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 9,12</t>
+          <t>0,5; 15,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 18,48</t>
+          <t>7,12; 18,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,67</t>
+          <t>-0,09; 10,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,22</t>
+          <t>4,06; 12,59</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107,55%</t>
+          <t>103,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-27,27%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>102,53%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>49,88; 292,67</t>
+          <t>51,02; 318,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 103,64</t>
+          <t>-32,22; 106,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,36; 231,98</t>
+          <t>32,68; 230,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,31; 593,24</t>
+          <t>11,42; 586,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 522,97</t>
+          <t>-3,2; 534,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,52; 142,53</t>
+          <t>0,39; 400,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,14; 289,96</t>
+          <t>61,46; 269,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 161,16</t>
+          <t>-1,31; 155,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,18; 130,48</t>
+          <t>34,68; 190,81</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 12,79</t>
+          <t>-10,36; 12,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 15,48</t>
+          <t>-5,47; 15,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 9,75</t>
+          <t>-12,24; 8,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 24,44</t>
+          <t>3,93; 25,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 14,0</t>
+          <t>-7,42; 13,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 17,74</t>
+          <t>0,06; 18,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,69</t>
+          <t>1,94; 19,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 11,58</t>
+          <t>-4,02; 11,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 14,42</t>
+          <t>-1,07; 13,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 183,2</t>
+          <t>-53,59; 178,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 229,9</t>
+          <t>-27,52; 232,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 158,33</t>
+          <t>-57,26; 128,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,29; 196,07</t>
+          <t>14,6; 196,97</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 112,28</t>
+          <t>-30,23; 101,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 152,6</t>
+          <t>-1,83; 147,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,92; 155,57</t>
+          <t>8,09; 176,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 90,57</t>
+          <t>-18,6; 95,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 127,26</t>
+          <t>-4,55; 113,94</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34,08</t>
+          <t>36,04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,59</t>
+          <t>14,02</t>
         </is>
       </c>
     </row>
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,0</t>
+          <t>0,0; 71,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,04; 17,68</t>
+          <t>6,05; 17,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,25; 15,89</t>
+          <t>4,6; 16,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,63; 18,45</t>
+          <t>8,34; 18,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,4; 17,16</t>
+          <t>5,8; 16,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,13; 16,47</t>
+          <t>4,65; 16,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,36</t>
+          <t>8,64; 18,84</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>102,86%</t>
+          <t>106,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>105,19%</t>
+          <t>108,46%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38,47; 166,43</t>
+          <t>38,85; 160,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26,66; 149,46</t>
+          <t>32,19; 150,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,54; 174,98</t>
+          <t>51,55; 176,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,46; 169,13</t>
+          <t>35,6; 157,91</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33,34; 158,14</t>
+          <t>28,08; 150,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54,52; 177,88</t>
+          <t>55,89; 181,86</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>7,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,81</t>
+          <t>3,02; 10,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 7,14</t>
+          <t>0,66; 7,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,19</t>
+          <t>1,39; 7,34</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,86; 16,41</t>
+          <t>8,16; 16,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,61</t>
+          <t>4,16; 12,93</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 10,49</t>
+          <t>6,09; 12,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,18; 13,13</t>
+          <t>7,01; 13,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,19</t>
+          <t>3,48; 9,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 8,32</t>
+          <t>4,74; 9,5</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>30,97; 170,19</t>
+          <t>29,97; 166,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1,2; 110,92</t>
+          <t>6,94; 116,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16,88; 131,75</t>
+          <t>15,42; 121,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48,14; 146,71</t>
+          <t>51,7; 147,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,6; 106,85</t>
+          <t>27,24; 115,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,01; 83,43</t>
+          <t>37,11; 114,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>55,76; 131,83</t>
+          <t>56,16; 135,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>27,21; 93,32</t>
+          <t>28,67; 96,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 82,82</t>
+          <t>36,1; 97,45</t>
         </is>
       </c>
     </row>
